--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104575_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104575_W13.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1935</v>
+        <v>5.4206</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5274</v>
+        <v>3.1075</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6661</v>
+        <v>2.3131</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9734</v>
+        <v>2.9656</v>
       </c>
       <c r="H2" t="n">
-        <v>2.283</v>
+        <v>2.2697</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6904</v>
+        <v>0.6959</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7728</v>
+        <v>2.748</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0638</v>
+        <v>2.0405</v>
       </c>
       <c r="L2" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2006</v>
+        <v>0.2176</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>4.0594</v>
+        <v>2.2973</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7281</v>
+        <v>1.34</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3313</v>
+        <v>0.9573</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9842</v>
+        <v>4.0508</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9703</v>
+        <v>4.3161</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0139</v>
+        <v>-0.2652</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5182</v>
+        <v>3.5113</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2841</v>
+        <v>2.2888</v>
       </c>
       <c r="I3" t="n">
-        <v>1.234</v>
+        <v>1.2225</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8957</v>
+        <v>3.8673</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1126</v>
+        <v>2.1029</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7831</v>
+        <v>1.7644</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3776</v>
+        <v>-0.356</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1715</v>
+        <v>0.1859</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5152</v>
+        <v>1.582</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2994</v>
+        <v>0.678</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2158</v>
+        <v>0.9039</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.4102</v>
+        <v>-2.4082</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.719</v>
+        <v>4.0418</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2708</v>
+        <v>3.8337</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4482</v>
+        <v>0.2081</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0795</v>
+        <v>3.4982</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.14</v>
+        <v>1.7172</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2195</v>
+        <v>1.781</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3557</v>
+        <v>4.1569</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1763</v>
+        <v>2.2063</v>
       </c>
       <c r="L4" t="n">
-        <v>4.1795</v>
+        <v>1.9505</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2762</v>
+        <v>-0.6587</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3162</v>
+        <v>-0.4891</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04</v>
+        <v>-0.1695</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2273</v>
+        <v>0.1974</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3176</v>
+        <v>-0.3232</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9097</v>
+        <v>0.5206</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3622</v>
+        <v>3.2247</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4392</v>
+        <v>1.001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.077</v>
+        <v>2.2236</v>
       </c>
       <c r="G5" t="n">
-        <v>3.505</v>
+        <v>4.0747</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7112</v>
+        <v>-0.1407</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7938</v>
+        <v>4.2154</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1862</v>
+        <v>4.3322</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2165</v>
+        <v>0.1616</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9697</v>
+        <v>4.1705</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6812</v>
+        <v>-0.2574</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5053</v>
+        <v>-0.3023</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1759</v>
+        <v>0.0449</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4773</v>
+        <v>0.7433</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.747</v>
+        <v>0.0834</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2698</v>
+        <v>0.66</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2794</v>
+        <v>2.9279</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3591</v>
+        <v>0.7837</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.07969999999999999</v>
+        <v>2.1442</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5581</v>
+        <v>-0.503</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6709</v>
+        <v>1.4679</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8871</v>
+        <v>-1.9709</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1011</v>
+        <v>-0.7771</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9395</v>
+        <v>1.5546</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1617</v>
+        <v>-2.3317</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5431</v>
+        <v>0.2741</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2685</v>
+        <v>-0.0866</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2745</v>
+        <v>0.3608</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7628</v>
+        <v>0.5203</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5263</v>
+        <v>0.4713</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2365</v>
+        <v>0.049</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8903</v>
+        <v>2.354</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0795</v>
+        <v>2.1684</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8107</v>
+        <v>0.1856</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4938</v>
+        <v>3.5526</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4733</v>
+        <v>1.6715</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.9672</v>
+        <v>1.8811</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.753</v>
+        <v>4.0826</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5687</v>
+        <v>1.9305</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.3218</v>
+        <v>2.1521</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2592</v>
+        <v>-0.53</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0954</v>
+        <v>-0.259</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3546</v>
+        <v>-0.271</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8147</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5232</v>
+        <v>0.8501</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2601</v>
+        <v>0.3622</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2631</v>
+        <v>0.4879</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4853</v>
+        <v>2.2795</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1009</v>
+        <v>0.847</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3844</v>
+        <v>1.4325</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6265</v>
+        <v>1.621</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8686</v>
+        <v>2.8665</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2422</v>
+        <v>-1.2455</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3245</v>
+        <v>1.3048</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8226</v>
+        <v>2.8096</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3019</v>
+        <v>0.3162</v>
       </c>
       <c r="N8" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1933</v>
+        <v>1.0047</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2087</v>
+        <v>0.5713</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4019</v>
+        <v>0.4335</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3938</v>
+        <v>1.8267</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5406</v>
+        <v>2.6964</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1468</v>
+        <v>-0.8696</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1309</v>
+        <v>2.1161</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.137</v>
+        <v>-1.1428</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2679</v>
+        <v>3.2589</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2362</v>
+        <v>3.2053</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6793</v>
+        <v>-0.697</v>
       </c>
       <c r="L9" t="n">
-        <v>3.9156</v>
+        <v>3.9022</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1053</v>
+        <v>-1.0891</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6859</v>
+        <v>-0.2486</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6956</v>
+        <v>-0.5089</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0097</v>
+        <v>0.2603</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3262</v>
+        <v>-0.0511</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0338</v>
+        <v>-0.6704</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7076</v>
+        <v>0.6194</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2797</v>
+        <v>-1.7548</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0132</v>
+        <v>-0.0265</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2665</v>
+        <v>-1.7282</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3451</v>
+        <v>-0.4355</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1212</v>
+        <v>0.9653</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2239</v>
+        <v>-1.4008</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6248</v>
+        <v>-1.3193</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1344</v>
+        <v>-0.9918</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4904</v>
+        <v>-0.3275</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8308</v>
+        <v>0.1103</v>
       </c>
       <c r="T10" t="n">
-        <v>0.248</v>
+        <v>-0.2349</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5828</v>
+        <v>0.3452</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5748</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5184</v>
+        <v>-0.3509</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0784</v>
+        <v>0.5454</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.8963</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7611</v>
+        <v>-1.2622</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0392</v>
+        <v>-1.0002</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.722</v>
+        <v>-0.262</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4191</v>
+        <v>0.3441</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9697</v>
+        <v>0.1207</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3888</v>
+        <v>0.2234</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.342</v>
+        <v>-1.6062</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0089</v>
+        <v>-1.1209</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3331</v>
+        <v>-0.4854</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3451</v>
+        <v>0.1405</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6593</v>
+        <v>-0.2232</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3142</v>
+        <v>0.3637</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5628</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. KEITA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8822</v>
+        <v>-1.6949</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.87</v>
+        <v>-1.5567</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0122</v>
+        <v>-0.1382</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2844</v>
+        <v>-2.7068</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3218</v>
+        <v>0.3247</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0373</v>
+        <v>-3.0315</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.749</v>
+        <v>-1.0152</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7864</v>
+        <v>1.3165</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0373</v>
+        <v>-2.3317</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5354</v>
+        <v>-1.6916</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5354</v>
+        <v>-0.9918</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0.6998</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0514</v>
+        <v>1.0998</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.121</v>
+        <v>0.5966</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0696</v>
+        <v>0.5032</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5463</v>
+        <v>-0.3155</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5463</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>S. KEITA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0574</v>
+        <v>-1.8102</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8533</v>
+        <v>-0.8036</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2042</v>
+        <v>-1.0066</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.7005</v>
+        <v>-1.284</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3276</v>
+        <v>-1.3212</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.0281</v>
+        <v>0.0372</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9853</v>
+        <v>-0.7524</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3365</v>
+        <v>-0.7896</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.3218</v>
+        <v>0.0372</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7152</v>
+        <v>-0.5315</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0089</v>
+        <v>-0.5315</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7063</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7377</v>
+        <v>0.0185</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2662</v>
+        <v>-0.0512</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4715</v>
+        <v>0.0697</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3214</v>
+        <v>-0.5447</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3214</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.1759</v>
+        <v>22.2189</v>
       </c>
       <c r="E14" t="n">
-        <v>15.5199</v>
+        <v>16.2685</v>
       </c>
       <c r="F14" t="n">
-        <v>5.655799999999999</v>
+        <v>5.950599999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>13.8721</v>
+        <v>13.8287</v>
       </c>
       <c r="H14" t="n">
-        <v>8.967500000000001</v>
+        <v>8.974900000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>4.904</v>
+        <v>4.853900000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>21.3109</v>
+        <v>21.061</v>
       </c>
       <c r="K14" t="n">
-        <v>13.8617</v>
+        <v>13.7219</v>
       </c>
       <c r="L14" t="n">
-        <v>7.449300000000003</v>
+        <v>7.338800000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.439100000000001</v>
+        <v>-7.2319</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.893899999999999</v>
+        <v>-4.746900000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.545</v>
+        <v>-2.485</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4025</v>
+        <v>3.414499999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.3417</v>
+        <v>-11.3817</v>
       </c>
       <c r="R14" t="n">
-        <v>14.7441</v>
+        <v>14.7961</v>
       </c>
       <c r="S14" t="n">
-        <v>7.2436</v>
+        <v>8.3156</v>
       </c>
       <c r="T14" t="n">
-        <v>1.693899999999999</v>
+        <v>2.7614</v>
       </c>
       <c r="U14" t="n">
-        <v>5.5497</v>
+        <v>5.5543</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.3421</v>
+        <v>-3.3398</v>
       </c>
       <c r="W14" t="n">
-        <v>3.8567</v>
+        <v>3.8281</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.198799999999999</v>
+        <v>-7.1677</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5453</v>
+        <v>2.808</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8717</v>
+        <v>3.8524</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3264</v>
+        <v>-1.0444</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1167</v>
+        <v>3.1262</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3161</v>
+        <v>-1.31</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4328</v>
+        <v>4.4362</v>
       </c>
       <c r="J15" t="n">
-        <v>4.776</v>
+        <v>4.7585</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1487</v>
+        <v>0.1411</v>
       </c>
       <c r="L15" t="n">
-        <v>4.6273</v>
+        <v>4.6174</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6593</v>
+        <v>-1.6323</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1593</v>
+        <v>-0.9116</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6775</v>
+        <v>-0.6785</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4818</v>
+        <v>-0.2331</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="16">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1868</v>
+        <v>2.248</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3602</v>
+        <v>1.3549</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8266</v>
+        <v>0.8931</v>
       </c>
       <c r="G16" t="n">
-        <v>1.443</v>
+        <v>1.4418</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1284</v>
+        <v>1.126</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8139</v>
+        <v>0.8101</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8139</v>
+        <v>0.8101</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1702,19 +1702,19 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1975</v>
+        <v>0.2614</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1975</v>
+        <v>0.2614</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4092</v>
+        <v>1.6198</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7674</v>
+        <v>1.8786</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3582</v>
+        <v>-0.2589</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1662</v>
+        <v>0.1668</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1284</v>
+        <v>1.126</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8139</v>
+        <v>0.8101</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8139</v>
+        <v>0.8101</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0765</v>
+        <v>0.1359</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1391</v>
+        <v>-0.021</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0626</v>
+        <v>0.1568</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3786</v>
+        <v>1.0411</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2613</v>
+        <v>0.7815</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1173</v>
+        <v>0.2597</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0189</v>
+        <v>0.0236</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6262</v>
+        <v>-0.6261</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6451</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1887</v>
+        <v>0.1811</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1141</v>
+        <v>0.1067</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1699</v>
+        <v>-0.1576</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5205</v>
+        <v>0.1754</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5263</v>
+        <v>0.0556</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0058</v>
+        <v>0.1198</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3327</v>
+        <v>1.0021</v>
       </c>
       <c r="E19" t="n">
-        <v>3.4097</v>
+        <v>3.0206</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.077</v>
+        <v>-2.0185</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4116</v>
+        <v>-1.4044</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.0563</v>
+        <v>-3.0505</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6446</v>
+        <v>1.6461</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9963</v>
+        <v>0.9767</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5683</v>
+        <v>-0.5795</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5646</v>
+        <v>1.5563</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4079</v>
+        <v>-2.3811</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.4879</v>
+        <v>-2.4709</v>
       </c>
       <c r="O19" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4676</v>
+        <v>-0.7921</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1089</v>
+        <v>-0.2442</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5765</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="W19" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3383</v>
+        <v>-2.179</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3317</v>
+        <v>-0.2264</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0066</v>
+        <v>-1.9527</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0328</v>
+        <v>-1.033</v>
       </c>
       <c r="H20" t="n">
-        <v>0.404</v>
+        <v>0.4076</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4368</v>
+        <v>-1.4406</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2248</v>
+        <v>0.2128</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4159</v>
+        <v>-0.4249</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2576</v>
+        <v>-1.2458</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2368</v>
+        <v>-0.2301</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3451</v>
+        <v>-0.1963</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5565</v>
+        <v>-0.4392</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2114</v>
+        <v>0.2429</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3978</v>
+        <v>-2.6913</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0115</v>
+        <v>0.0664</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3864</v>
+        <v>-2.7577</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1811</v>
+        <v>0.1876</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7301</v>
+        <v>0.7295</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="J21" t="n">
-        <v>3.1331</v>
+        <v>3.1094</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0536</v>
+        <v>2.0372</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.952</v>
+        <v>-2.9218</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3234</v>
+        <v>-1.3077</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6285</v>
+        <v>-1.6141</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0838</v>
+        <v>-0.375</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8347</v>
+        <v>-0.718</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7509</v>
+        <v>0.343</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>J. SORIANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8878</v>
+        <v>-3.5212</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3653</v>
+        <v>-0.9555</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5225</v>
+        <v>-2.5657</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4135</v>
+        <v>-1.9922</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6623</v>
+        <v>-1.1139</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7512</v>
+        <v>-0.8783</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2958</v>
+        <v>0.8309</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0075</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7117</v>
+        <v>0.1489</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7092</v>
+        <v>-2.8232</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6698</v>
+        <v>-1.7959</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7277</v>
+        <v>-0.6004</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3266</v>
+        <v>-0.6483</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4011</v>
+        <v>0.0479</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1607</v>
+        <v>-0.4733</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. SORIANO</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.961</v>
+        <v>-3.8973</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0441</v>
+        <v>-2.7533</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9169</v>
+        <v>-1.144</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9954</v>
+        <v>-2.4059</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1052</v>
+        <v>-0.6634</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8902</v>
+        <v>-1.7425</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.2738</v>
       </c>
       <c r="K23" t="n">
-        <v>0.706</v>
+        <v>0.989</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1493</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.8506</v>
+        <v>-2.6797</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8112</v>
+        <v>-1.6524</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0298</v>
+        <v>-0.7387</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7652</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2646</v>
+        <v>-0.0578</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.4822</v>
+        <v>0.1578</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.4822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0891</v>
+        <v>-4.6316</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4434</v>
+        <v>-2.3626</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6457</v>
+        <v>-2.269</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.4359</v>
+        <v>-3.4377</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.7188</v>
+        <v>-2.717</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2889</v>
+        <v>-1.3172</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9028</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.2098</v>
+        <v>-2.22</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.147</v>
+        <v>-2.1205</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.638</v>
+        <v>-1.6235</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.88</v>
+        <v>-1.4216</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8861</v>
+        <v>-0.7692</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9938</v>
+        <v>-0.6524</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.4311</v>
+        <v>-4.8355</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7643</v>
+        <v>-3.5431</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6668</v>
+        <v>-1.2924</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.975</v>
+        <v>-2.9551</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.0665</v>
+        <v>-1.0547</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.9085</v>
+        <v>-1.9004</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3134</v>
+        <v>-0.3187</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3983</v>
+        <v>0.3964</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.6615</v>
+        <v>-2.6364</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5488</v>
+        <v>-0.9699</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9557</v>
+        <v>-0.7204</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5931</v>
+        <v>-0.2494</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.9233</v>
+        <v>-6.5572</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.2734</v>
+        <v>-5.9744</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6499</v>
+        <v>-0.5828</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.5337</v>
+        <v>-5.5466</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.8091</v>
+        <v>-3.8248</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.7246</v>
+        <v>-1.7219</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.0563</v>
+        <v>-3.0958</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.1553</v>
+        <v>-2.1868</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.901</v>
+        <v>-0.909</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.4774</v>
+        <v>-2.4508</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.6539</v>
+        <v>-1.638</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.643</v>
+        <v>-0.2579</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.0434</v>
+        <v>-0.6902</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4004</v>
+        <v>0.4324</v>
       </c>
       <c r="V26" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W26" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-21.1758</v>
+        <v>-19.5941</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.5634</v>
+        <v>-4.860899999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-16.6125</v>
+        <v>-14.7333</v>
       </c>
       <c r="G27" t="n">
-        <v>-13.872</v>
+        <v>-13.8289</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.9679</v>
+        <v>-8.975</v>
       </c>
       <c r="I27" t="n">
-        <v>-4.9043</v>
+        <v>-4.853899999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>7.4392</v>
+        <v>7.231699999999998</v>
       </c>
       <c r="K27" t="n">
-        <v>4.894</v>
+        <v>4.7469</v>
       </c>
       <c r="L27" t="n">
-        <v>2.545199999999999</v>
+        <v>2.484999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>-21.311</v>
+        <v>-21.0608</v>
       </c>
       <c r="N27" t="n">
-        <v>-13.862</v>
+        <v>-13.7217</v>
       </c>
       <c r="O27" t="n">
-        <v>-7.449400000000001</v>
+        <v>-7.3389</v>
       </c>
       <c r="P27" t="n">
-        <v>-3.4024</v>
+        <v>-3.414299999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>-14.7443</v>
+        <v>-14.796</v>
       </c>
       <c r="R27" t="n">
-        <v>11.3415</v>
+        <v>11.3815</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.2436</v>
+        <v>-5.6908</v>
       </c>
       <c r="T27" t="n">
-        <v>-5.5496</v>
+        <v>-5.554299999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.6939</v>
+        <v>-0.1364</v>
       </c>
       <c r="V27" t="n">
-        <v>3.342099999999999</v>
+        <v>3.34</v>
       </c>
       <c r="W27" t="n">
-        <v>8.291499999999999</v>
+        <v>8.257399999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>-4.949400000000001</v>
+        <v>-4.9176</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104575_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104575_W13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.1677</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104575_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-4.9176</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
